--- a/slides/장학사_엑셀/실습데이터/예제1_방과후학교_1줄머리글/원본/나래초등학교.xlsx
+++ b/slides/장학사_엑셀/실습데이터/예제1_방과후학교_1줄머리글/원본/나래초등학교.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -484,7 +484,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>담당: 이나래 (2025. 3. 12.)</t>
+          <t>담당: 이나래 (2025. 3. 17.)</t>
         </is>
       </c>
     </row>
@@ -518,82 +518,156 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>영어회화</t>
+          <t>과학실험</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>독서논술</t>
+          <t>영어회화</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>24</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>예체능</t>
-        </is>
-      </c>
+      <c r="A7" s="7" t="n"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>방송댄스</t>
+          <t>한자교실</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>축구교실</t>
+          <t>한국사</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
         <v>28</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>피아노</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>바이올린</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>방송댄스</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>미술교실</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>로봇과학</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="9" t="n">
-        <v>104</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>109</v>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="9" t="n">
+        <v>220</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>321</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A5:A8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/slides/장학사_엑셀/실습데이터/예제1_방과후학교_1줄머리글/원본/나래초등학교.xlsx
+++ b/slides/장학사_엑셀/실습데이터/예제1_방과후학교_1줄머리글/원본/나래초등학교.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="방과후" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="방과후" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,11 +38,11 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -85,21 +85,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -488,177 +489,184 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>지역: 동부    설립: 사립</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>영역</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>강좌명</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>1학기</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>2학기</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>과학실험</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="7" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n"/>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>영어회화</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <v>76</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>한자교실</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="7" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>한국사</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="7" t="n">
         <v>53</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>피아노</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="7" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>바이올린</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="7" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>방송댄스</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="7" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>미술교실</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="7" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>로봇과학</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="7" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="9" t="n">
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="10" t="n">
         <v>220</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="10" t="n">
         <v>321</v>
       </c>
     </row>
